--- a/outputs/mrv-operational-documents/Charm_BioOil_SAF_CI_Calculator_EU205_2026-07-23.xlsx
+++ b/outputs/mrv-operational-documents/Charm_BioOil_SAF_CI_Calculator_EU205_2026-07-23.xlsx
@@ -107,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -161,6 +161,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -526,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -557,7 +562,11 @@
           <t>12-month actual-value CI (Apr 2025 – Mar 2026) from the Final Reporting Package PP Summaries  |  built/updated 2026-07-23</t>
         </is>
       </c>
-      <c r="C3" s="25" t="n"/>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>12-month actual-value CI (Apr 2025 – Mar 2026) from the Final Reporting Package PP Summaries, on METERED activity data  |  built 2026-07-23, metered basis applied 2026-07-28</t>
+        </is>
+      </c>
       <c r="D3" s="25" t="n"/>
     </row>
     <row r="4">
@@ -575,7 +584,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Bio-oil CI = 569 kgCO2eq/tonne = 37.9 gCO2eq/MJ (Result tab / EU205_CI). Live off PP_Data — updates if any input changes.</t>
+          <t>Bio-oil CI = 560 kgCO2eq/tonne = 37.36 gCO2eq/MJ (Result tab / EU205_CI). Live off PP_Data — updates if any input changes.</t>
         </is>
       </c>
       <c r="D5" s="25" t="n"/>
@@ -659,56 +668,63 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>e_ec = 0 (feedstock argued as waste, RED Annex V); BCU (renewable-diesel book-and-claim) and REC excluded → gross diesel + grid electricity; equipment embodied excluded (EU 205 p.11/17); water/consumables/waste/tailgas excluded under the 0.5% materiality rule. Full basis + citations on Source_Inclusion.</t>
+          <t>e_ec = 0 (feedstock argued as waste, RED Annex V); BCU (renewable-diesel book-and-claim) and REC excluded → gross diesel + grid electricity; equipment embodied excluded (EU 205 p.11/17); water/consumables/waste/tailgas excluded under the §4.1 p.20 0.5% rule. Full basis + citations on Source_Inclusion.</t>
         </is>
       </c>
       <c r="D11" s="25" t="n"/>
     </row>
     <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="25" t="n"/>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Allocation</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Bio-oil (WODO + Aqueous, no sub-split) vs biochar split by energy content (EU 205 §4.3.8), from measured LHVs (bio-oil ~15; biochar 22.8 derived from SGS GCV).</t>
-        </is>
-      </c>
-      <c r="D12" s="25" t="n"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Measurement basis</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>All fuel and electricity quantities are the METERED figures from the PP Summaries. The Summaries' "Uncertainty Adjusted Total" columns (fuels +1.29%, electricity +2.00%) are deliberately not used: EU 205 §4.1 p.20 calls for "Actual data measured and gathered at the system user", and the document (read in full, pp.2-67) has no meter-uncertainty adjustment provision. Using the adjusted columns would give 37.94 gCO2eq/MJ instead of 37.36. Full basis on Source_Inclusion.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="25" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>Allocation</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Bio-oil (WODO + Aqueous, no sub-split) vs biochar split by energy content (EU 205 §4.3.8), from measured LHVs (bio-oil ~15; biochar 22.8 derived from SGS GCV).</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="n"/>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="25" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
           <t>Open refinements</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>(1) electricity uses the U.S. national eGRID rate for all months (single national factor, per your instruction); (2) e_td uses Charm's calculated gross biomass-transport per period; (3) refinery→SAF tab is a placeholder pending real data.</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n"/>
-    </row>
-    <row r="14" ht="46" customHeight="1">
-      <c r="B14" s="3" t="inlineStr">
+      <c r="D14" s="25" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Colour legend</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>YELLOW = pulled activity data  |  GREEN = calculated (formula)  |  BLUE = sourced constant  |  ORANGE = placeholder.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>(1) electricity uses the U.S. national eGRID rate for all months (single national factor, per your instruction); (2) e_td uses Charm's calculated gross biomass-transport per period; (3) refinery→SAF tab is a placeholder pending real data.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -720,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:P17"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -751,7 +767,7 @@
     <row r="2" ht="44" customHeight="1">
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Bio-oil = WODO + Aqueous (no sub-split). Activity taken from each month's Final Reporting Package Production Period Summary; Charm's emission columns NOT copied — emissions are recomputed under EU 205. Totals = live SUM.</t>
+          <t>Bio-oil = WODO + Aqueous (no sub-split). Activity taken from each month's Final Reporting Package Production Period Summary. ALL fuel and electricity inputs are the METERED figures — the PP Summaries' "Uncertainty Adjusted Total" / "Total kWh Consumed -- Uncertainty Adjusted" columns are deliberately NOT used (see Source_Inclusion, "Measurement basis"). Charm's emission columns are not copied either — emissions are recomputed under EU 205. Totals = live SUM.</t>
         </is>
       </c>
     </row>
@@ -887,7 +903,7 @@
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Biomass consumed</t>
+          <t>Biomass consumed (PP Summary labels this "Uncertainty-Adjusted"; not used in the CI)</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -939,7 +955,7 @@
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Propane used (unc-adj)</t>
+          <t>Propane used — metered</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -948,40 +964,40 @@
         </is>
       </c>
       <c r="D7" s="16" t="n">
-        <v>5744.56</v>
+        <v>5671.4</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>6128.37</v>
+        <v>6050.32</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>6315.33</v>
+        <v>6234.9</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>7882.08</v>
+        <v>7781.7</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>5568.17</v>
+        <v>5497.25</v>
       </c>
       <c r="I7" s="16" t="n">
-        <v>3141.64</v>
+        <v>3101.63</v>
       </c>
       <c r="J7" s="16" t="n">
-        <v>4396.12</v>
+        <v>4340.13</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>3925.52</v>
+        <v>3875.53</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>2782.65</v>
+        <v>2747.21</v>
       </c>
       <c r="M7" s="16" t="n">
-        <v>3623.46</v>
+        <v>3577.31</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>3939.83</v>
+        <v>3889.65</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>4290.88</v>
+        <v>4236.23</v>
       </c>
       <c r="P7" s="18">
         <f>SUM(D7:O7)</f>
@@ -991,7 +1007,7 @@
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Diesel — production (unc-adj)</t>
+          <t>Diesel — production, metered</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -1000,40 +1016,40 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>3617.22</v>
+        <v>3571.15</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>1057.79</v>
+        <v>1044.32</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>5161.86</v>
+        <v>5096.12</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>8867.07</v>
+        <v>8754.139999999999</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>6090.93</v>
+        <v>6013.36</v>
       </c>
       <c r="I8" s="16" t="n">
-        <v>729.96</v>
+        <v>720.66</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>3952.86</v>
+        <v>3902.52</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>4376.51</v>
+        <v>4320.77</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>5109.73</v>
+        <v>5044.65</v>
       </c>
       <c r="M8" s="16" t="n">
-        <v>4868.57</v>
+        <v>4806.57</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>3203.36</v>
+        <v>3162.56</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>2902.57</v>
+        <v>2865.6</v>
       </c>
       <c r="P8" s="18">
         <f>SUM(D8:O8)</f>
@@ -1043,7 +1059,7 @@
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Gasoline (unc-adj)</t>
+          <t>Gasoline — metered</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
@@ -1052,40 +1068,40 @@
         </is>
       </c>
       <c r="D9" s="16" t="n">
-        <v>290.13</v>
+        <v>286.43</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>133.26</v>
+        <v>131.56</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>163.23</v>
+        <v>161.15</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>28</v>
+        <v>27.64</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>56.04</v>
+        <v>55.33</v>
       </c>
       <c r="I9" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="16" t="n">
-        <v>135.88</v>
+        <v>134.15</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>134.32</v>
+        <v>132.61</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>97.63</v>
+        <v>96.39</v>
       </c>
       <c r="M9" s="16" t="n">
-        <v>109.8</v>
+        <v>108.4</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>139.98</v>
+        <v>138.2</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>120.03</v>
+        <v>118.5</v>
       </c>
       <c r="P9" s="18">
         <f>SUM(D9:O9)</f>
@@ -1095,7 +1111,7 @@
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Electricity — production</t>
+          <t>Electricity — total site, metered</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
@@ -1104,40 +1120,40 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>56352.7</v>
+        <v>63987.78</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>45185.05</v>
+        <v>53330.44</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>43444.3</v>
+        <v>51332.49</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>50821.57</v>
+        <v>58856.44</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>45947.77</v>
+        <v>54078.21</v>
       </c>
       <c r="I10" s="16" t="n">
-        <v>35385.95</v>
+        <v>43432.15</v>
       </c>
       <c r="J10" s="16" t="n">
-        <v>38806.94</v>
+        <v>47077.39</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>36751.05</v>
+        <v>44770.48</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>25041.26</v>
+        <v>33581.63</v>
       </c>
       <c r="M10" s="16" t="n">
-        <v>35161.91</v>
+        <v>43503.83</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>35984.82</v>
+        <v>43436.6</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>38417</v>
+        <v>46695.1</v>
       </c>
       <c r="P10" s="18">
         <f>SUM(D10:O10)</f>
@@ -1145,176 +1161,219 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Electricity — non-production carve-out</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>kWh</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="n">
+        <v>8914.84</v>
+      </c>
+      <c r="E11" s="28" t="n">
+        <v>9212</v>
+      </c>
+      <c r="F11" s="28" t="n">
+        <v>8914.84</v>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>9212</v>
+      </c>
+      <c r="H11" s="28" t="n">
+        <v>9212</v>
+      </c>
+      <c r="I11" s="28" t="n">
+        <v>8914.84</v>
+      </c>
+      <c r="J11" s="28" t="n">
+        <v>9212</v>
+      </c>
+      <c r="K11" s="28" t="n">
+        <v>8914.84</v>
+      </c>
+      <c r="L11" s="28" t="n">
+        <v>9212</v>
+      </c>
+      <c r="M11" s="28" t="n">
+        <v>9212</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>8320.52</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>9212</v>
+      </c>
+      <c r="P11" s="29">
+        <f>SUM(D11:O11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Electricity — production (= total metered − carve-out)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>kWh</t>
+        </is>
+      </c>
+      <c r="D12" s="29">
+        <f>D10-D11</f>
+        <v/>
+      </c>
+      <c r="E12" s="29">
+        <f>E10-E11</f>
+        <v/>
+      </c>
+      <c r="F12" s="29">
+        <f>F10-F11</f>
+        <v/>
+      </c>
+      <c r="G12" s="29">
+        <f>G10-G11</f>
+        <v/>
+      </c>
+      <c r="H12" s="29">
+        <f>H10-H11</f>
+        <v/>
+      </c>
+      <c r="I12" s="29">
+        <f>I10-I11</f>
+        <v/>
+      </c>
+      <c r="J12" s="29">
+        <f>J10-J11</f>
+        <v/>
+      </c>
+      <c r="K12" s="29">
+        <f>K10-K11</f>
+        <v/>
+      </c>
+      <c r="L12" s="29">
+        <f>L10-L11</f>
+        <v/>
+      </c>
+      <c r="M12" s="29">
+        <f>M10-M11</f>
+        <v/>
+      </c>
+      <c r="N12" s="29">
+        <f>N10-N11</f>
+        <v/>
+      </c>
+      <c r="O12" s="29">
+        <f>O10-O11</f>
+        <v/>
+      </c>
+      <c r="P12" s="29">
+        <f>SUM(D12:O12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Water consumed</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D13" s="16" t="n">
         <v>84514.92</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E13" s="16" t="n">
         <v>61277.67</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F13" s="16" t="n">
         <v>73596.38</v>
       </c>
-      <c r="G11" s="16" t="n">
+      <c r="G13" s="16" t="n">
         <v>82966.74000000001</v>
       </c>
-      <c r="H11" s="16" t="n">
+      <c r="H13" s="16" t="n">
         <v>68468.36</v>
       </c>
-      <c r="I11" s="16" t="n">
+      <c r="I13" s="16" t="n">
         <v>27302.59</v>
       </c>
-      <c r="J11" s="16" t="n">
+      <c r="J13" s="16" t="n">
         <v>26027.64</v>
       </c>
-      <c r="K11" s="16" t="n">
+      <c r="K13" s="16" t="n">
         <v>24702.61</v>
       </c>
-      <c r="L11" s="16" t="n">
+      <c r="L13" s="16" t="n">
         <v>17234.72</v>
       </c>
-      <c r="M11" s="16" t="n">
+      <c r="M13" s="16" t="n">
         <v>18119.16</v>
       </c>
-      <c r="N11" s="16" t="n">
+      <c r="N13" s="16" t="n">
         <v>26051.02</v>
       </c>
-      <c r="O11" s="16" t="n">
+      <c r="O13" s="16" t="n">
         <v>27379.19</v>
       </c>
-      <c r="P11" s="18">
-        <f>SUM(D11:O11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Biomass transport (gross, pre-BCU)</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>MT CO2e</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="H12" s="16" t="n">
-        <v>1.639</v>
-      </c>
-      <c r="I12" s="16" t="n">
-        <v>2.927</v>
-      </c>
-      <c r="J12" s="16" t="n">
-        <v>1.452</v>
-      </c>
-      <c r="K12" s="16" t="n">
-        <v>1.844</v>
-      </c>
-      <c r="L12" s="16" t="n">
-        <v>2.167</v>
-      </c>
-      <c r="M12" s="16" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="N12" s="16" t="n">
-        <v>1.798</v>
-      </c>
-      <c r="O12" s="16" t="n">
-        <v>2.228</v>
-      </c>
-      <c r="P12" s="18">
-        <f>SUM(D12:O12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>OUTPUTS</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr"/>
-      <c r="D13" s="19" t="inlineStr"/>
-      <c r="E13" s="19" t="inlineStr"/>
-      <c r="F13" s="19" t="inlineStr"/>
-      <c r="G13" s="19" t="inlineStr"/>
-      <c r="H13" s="19" t="inlineStr"/>
-      <c r="I13" s="19" t="inlineStr"/>
-      <c r="J13" s="19" t="inlineStr"/>
-      <c r="K13" s="19" t="inlineStr"/>
-      <c r="L13" s="19" t="inlineStr"/>
-      <c r="M13" s="19" t="inlineStr"/>
-      <c r="N13" s="19" t="inlineStr"/>
-      <c r="O13" s="19" t="inlineStr"/>
-      <c r="P13" s="19" t="inlineStr"/>
+      <c r="P13" s="18">
+        <f>SUM(D13:O13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>WODO yield</t>
+          <t>Biomass transport (gross, pre-BCU)</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>MT CO2e</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>22298</v>
+        <v>3.19</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>25890</v>
+        <v>4.32</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>16899</v>
+        <v>5.02</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>22732</v>
+        <v>2.86</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>20928</v>
+        <v>1.639</v>
       </c>
       <c r="I14" s="16" t="n">
-        <v>12630</v>
+        <v>2.927</v>
       </c>
       <c r="J14" s="16" t="n">
-        <v>14227</v>
+        <v>1.452</v>
       </c>
       <c r="K14" s="16" t="n">
-        <v>9984</v>
+        <v>1.844</v>
       </c>
       <c r="L14" s="16" t="n">
-        <v>6481</v>
+        <v>2.167</v>
       </c>
       <c r="M14" s="16" t="n">
-        <v>8888</v>
+        <v>2.365</v>
       </c>
       <c r="N14" s="16" t="n">
-        <v>10966</v>
+        <v>1.798</v>
       </c>
       <c r="O14" s="16" t="n">
-        <v>16307</v>
+        <v>2.228</v>
       </c>
       <c r="P14" s="18">
         <f>SUM(D14:O14)</f>
@@ -1322,61 +1381,30 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Aqueous yield</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>75500</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>75500</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>75500</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>77076</v>
-      </c>
-      <c r="H15" s="16" t="n">
-        <v>75500</v>
-      </c>
-      <c r="I15" s="16" t="n">
-        <v>75500</v>
-      </c>
-      <c r="J15" s="16" t="n">
-        <v>75500</v>
-      </c>
-      <c r="K15" s="16" t="n">
-        <v>40930</v>
-      </c>
-      <c r="L15" s="16" t="n">
-        <v>19161</v>
-      </c>
-      <c r="M15" s="16" t="n">
-        <v>30830</v>
-      </c>
-      <c r="N15" s="16" t="n">
-        <v>37126</v>
-      </c>
-      <c r="O15" s="16" t="n">
-        <v>46683</v>
-      </c>
-      <c r="P15" s="18">
-        <f>SUM(D15:O15)</f>
-        <v/>
-      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>OUTPUTS</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr"/>
+      <c r="D15" s="19" t="inlineStr"/>
+      <c r="E15" s="19" t="inlineStr"/>
+      <c r="F15" s="19" t="inlineStr"/>
+      <c r="G15" s="19" t="inlineStr"/>
+      <c r="H15" s="19" t="inlineStr"/>
+      <c r="I15" s="19" t="inlineStr"/>
+      <c r="J15" s="19" t="inlineStr"/>
+      <c r="K15" s="19" t="inlineStr"/>
+      <c r="L15" s="19" t="inlineStr"/>
+      <c r="M15" s="19" t="inlineStr"/>
+      <c r="N15" s="19" t="inlineStr"/>
+      <c r="O15" s="19" t="inlineStr"/>
+      <c r="P15" s="19" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Biochar yield</t>
+          <t>WODO yield</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -1385,40 +1413,40 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>11426</v>
+        <v>22298</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>10357</v>
+        <v>25890</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>10309</v>
+        <v>16899</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>11597</v>
+        <v>22732</v>
       </c>
       <c r="H16" s="16" t="n">
-        <v>9186</v>
+        <v>20928</v>
       </c>
       <c r="I16" s="16" t="n">
-        <v>3868</v>
+        <v>12630</v>
       </c>
       <c r="J16" s="16" t="n">
-        <v>8085</v>
+        <v>14227</v>
       </c>
       <c r="K16" s="16" t="n">
-        <v>4580</v>
+        <v>9984</v>
       </c>
       <c r="L16" s="16" t="n">
-        <v>4074</v>
+        <v>6481</v>
       </c>
       <c r="M16" s="16" t="n">
-        <v>6560</v>
+        <v>8888</v>
       </c>
       <c r="N16" s="16" t="n">
-        <v>6766</v>
+        <v>10966</v>
       </c>
       <c r="O16" s="16" t="n">
-        <v>6259</v>
+        <v>16307</v>
       </c>
       <c r="P16" s="18">
         <f>SUM(D16:O16)</f>
@@ -1426,9 +1454,9 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Bio-oil (WODO+Aqueous)</t>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Aqueous yield</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
@@ -1436,56 +1464,160 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D17" s="20">
-        <f>D14+D15</f>
-        <v/>
-      </c>
-      <c r="E17" s="20">
-        <f>E14+E15</f>
-        <v/>
-      </c>
-      <c r="F17" s="20">
-        <f>F14+F15</f>
-        <v/>
-      </c>
-      <c r="G17" s="20">
-        <f>G14+G15</f>
-        <v/>
-      </c>
-      <c r="H17" s="20">
-        <f>H14+H15</f>
-        <v/>
-      </c>
-      <c r="I17" s="20">
-        <f>I14+I15</f>
-        <v/>
-      </c>
-      <c r="J17" s="20">
-        <f>J14+J15</f>
-        <v/>
-      </c>
-      <c r="K17" s="20">
-        <f>K14+K15</f>
-        <v/>
-      </c>
-      <c r="L17" s="20">
-        <f>L14+L15</f>
-        <v/>
-      </c>
-      <c r="M17" s="20">
-        <f>M14+M15</f>
-        <v/>
-      </c>
-      <c r="N17" s="20">
-        <f>N14+N15</f>
-        <v/>
-      </c>
-      <c r="O17" s="20">
-        <f>O14+O15</f>
-        <v/>
+      <c r="D17" s="16" t="n">
+        <v>75500</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>75500</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>75500</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>77076</v>
+      </c>
+      <c r="H17" s="16" t="n">
+        <v>75500</v>
+      </c>
+      <c r="I17" s="16" t="n">
+        <v>75500</v>
+      </c>
+      <c r="J17" s="16" t="n">
+        <v>75500</v>
+      </c>
+      <c r="K17" s="16" t="n">
+        <v>40930</v>
+      </c>
+      <c r="L17" s="16" t="n">
+        <v>19161</v>
+      </c>
+      <c r="M17" s="16" t="n">
+        <v>30830</v>
+      </c>
+      <c r="N17" s="16" t="n">
+        <v>37126</v>
+      </c>
+      <c r="O17" s="16" t="n">
+        <v>46683</v>
       </c>
       <c r="P17" s="18">
         <f>SUM(D17:O17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Biochar yield</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>11426</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>10357</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <v>10309</v>
+      </c>
+      <c r="G18" s="16" t="n">
+        <v>11597</v>
+      </c>
+      <c r="H18" s="16" t="n">
+        <v>9186</v>
+      </c>
+      <c r="I18" s="16" t="n">
+        <v>3868</v>
+      </c>
+      <c r="J18" s="16" t="n">
+        <v>8085</v>
+      </c>
+      <c r="K18" s="16" t="n">
+        <v>4580</v>
+      </c>
+      <c r="L18" s="16" t="n">
+        <v>4074</v>
+      </c>
+      <c r="M18" s="16" t="n">
+        <v>6560</v>
+      </c>
+      <c r="N18" s="16" t="n">
+        <v>6766</v>
+      </c>
+      <c r="O18" s="16" t="n">
+        <v>6259</v>
+      </c>
+      <c r="P18" s="18">
+        <f>SUM(D18:O18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Bio-oil (WODO+Aqueous)</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D19" s="20">
+        <f>D16+D17</f>
+        <v/>
+      </c>
+      <c r="E19" s="20">
+        <f>E16+E17</f>
+        <v/>
+      </c>
+      <c r="F19" s="20">
+        <f>F16+F17</f>
+        <v/>
+      </c>
+      <c r="G19" s="20">
+        <f>G16+G17</f>
+        <v/>
+      </c>
+      <c r="H19" s="20">
+        <f>H16+H17</f>
+        <v/>
+      </c>
+      <c r="I19" s="20">
+        <f>I16+I17</f>
+        <v/>
+      </c>
+      <c r="J19" s="20">
+        <f>J16+J17</f>
+        <v/>
+      </c>
+      <c r="K19" s="20">
+        <f>K16+K17</f>
+        <v/>
+      </c>
+      <c r="L19" s="20">
+        <f>L16+L17</f>
+        <v/>
+      </c>
+      <c r="M19" s="20">
+        <f>M16+M17</f>
+        <v/>
+      </c>
+      <c r="N19" s="20">
+        <f>N16+N17</f>
+        <v/>
+      </c>
+      <c r="O19" s="20">
+        <f>O16+O17</f>
+        <v/>
+      </c>
+      <c r="P19" s="18">
+        <f>SUM(D19:O19)</f>
         <v/>
       </c>
     </row>
@@ -1500,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E19"/>
+  <dimension ref="B1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1520,7 +1652,7 @@
     <row r="2" ht="54" customHeight="1">
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Each source is judged against the primary text. Materiality rule (Max-directed): a source contributing &lt;0.5% of the EU-205 recomputed period total may be excluded, with the source and its % stated. This is a disclosed simplification — EU 205's formula itself carries no de minimis, so exclusions are conservative and reversible (one cell).</t>
+          <t>Each source is judged against the primary text. Materiality: EU 205 §4.1 p.20 permits exclusion of small inputs — verbatim: "If an input has little or no effect for the emission element of the calculation formula, it can be excluded from the emission calculation. Inputs with little or no effect are those that have an impact on the overall emissions of the respective calculation formula element (e.g. cultivation eec) that is lower than 0.5%." NOTE: p.20 measures the 0.5% against the individual formula element; the percentages recorded below are against the period total, so they are an approximation of that test. Exclusions are reversible (one cell).</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1828,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Grid electricity at the U.S. NATIONAL grid EF — NOT the REC-adjusted figure. EU 205 §4.3.5.1 (pp.47-48): 'the EF of the national/country electricity mix shall be used' unless a direct metered renewable connection exists. U.S. national eGRID2023 total-output = 0.34968 kgCO2e/kWh (770.9 lb CO2e/MWh); Charm's REC-netted ~0.037 figure is dropped.</t>
+          <t>Grid electricity at the U.S. NATIONAL grid EF — NOT the REC-adjusted figure. EU 205 §4.3.5.1 p.47: "If electricity is consumed from the grid, the EF of the national/country electricity mix (EFelectricity) shall be used." U.S. national eGRID2023 total-output = 0.34968 kgCO2e/kWh (770.9 lb CO2e/MWh). Quantity is the METERED total kWh less the non-production carve-out — the PP Summary's 2.00% "Maximum Allowable Meter Uncertainty" uplift is not applied. Charm's REC-netted ~0.037 figure is dropped.</t>
         </is>
       </c>
     </row>
@@ -1873,6 +2005,28 @@
       <c r="E19" s="4" t="inlineStr">
         <is>
           <t>No book-and-claim REC pathway in EU 205; grid EF required (§4.3.5.1). See Electricity row — the REC credit is dropped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>Measurement basis — metered vs meter-uncertainty-adjusted</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>METERED (adjusted figures not used)</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>e_p quantities</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="inlineStr">
+        <is>
+          <t>The PP Summaries report each fuel twice — the metered quantity, then an "Uncertainty Adjusted Total" uplifted by "Fuel Meter Uncertainty" 1.29% (electricity: "Maximum Allowable Meter Uncertainty" 2.00%). This calculator uses the METERED figure. Basis: EU 205 §4.1 p.20 — "Actual data measured and gathered at the system user must be documented and provided to the auditor for the verification"; §4.3.5.2 p.49 — "the respective quantities must be extracted from respective operating documents for the previous year and must be verified by the auditors", listing "Electricity consumption in kWh/yr". EU 205 v4.1 was read end to end (pp.2-67) and contains no provision for adjusting measured activity data for meter uncertainty in either direction; its conservatism rules (§3.2 p.16, §4.3.1 p.22, §4.3.7 p.53, §4.3.9 p.57) all govern choice among published values or batches, not scaling of a metered quantity. Using the adjusted column would raise the CI by 0.58 gCO2eq/MJ (37.94 vs 37.36) — conservative, but not the measured value. Biomass is the one input with no separate metered figure in the source; it is retained as reported and does not feed the CI (it drove tailgas only, which is excluded).</t>
         </is>
       </c>
     </row>
@@ -1906,7 +2060,7 @@
     <row r="2" ht="44" customHeight="1">
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Emissions rebuilt from summed activity with Annex IX EFs, U.S. national grid electricity (no REC), gross-of-BCU. e_ec=0 (feedstock argued as waste). Excluded: equipment embodied, BCU, REC, water/consumables/waste/tailgas (&lt;0.5%). Live formulas.</t>
+          <t>Emissions rebuilt from summed METERED activity with Annex IX EFs, U.S. national grid electricity (no REC), gross-of-BCU. Meter-uncertainty-adjusted figures are NOT used — EU 205 §4.1 p.20 requires "Actual data measured and gathered at the system user". e_ec=0 (feedstock argued as waste). Excluded: equipment embodied, BCU, REC, water/consumables/waste/tailgas. Live formulas.</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2334,7 @@
         </is>
       </c>
       <c r="C23" s="8">
-        <f>PP_Data!P10*C11</f>
+        <f>PP_Data!P12*C11</f>
         <v/>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -2211,7 +2365,7 @@
         </is>
       </c>
       <c r="C25" s="8">
-        <f>PP_Data!P12*1000</f>
+        <f>PP_Data!P14*1000</f>
         <v/>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2238,7 +2392,7 @@
         </is>
       </c>
       <c r="C28" s="8">
-        <f>PP_Data!P17*C12</f>
+        <f>PP_Data!P19*C12</f>
         <v/>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -2254,7 +2408,7 @@
         </is>
       </c>
       <c r="C29" s="8">
-        <f>PP_Data!P16*C16</f>
+        <f>PP_Data!P18*C16</f>
         <v/>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2297,7 +2451,7 @@
         </is>
       </c>
       <c r="C33" s="10">
-        <f>IFERROR(C31/(PP_Data!P17/1000),"")</f>
+        <f>IFERROR(C31/(PP_Data!P19/1000),"")</f>
         <v/>
       </c>
     </row>
@@ -2313,7 +2467,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>12-mo Apr 2025 – Mar 2026 (all 12 months produced)</t>
+          <t>12-mo Apr 2025 – Mar 2026 (all 12 months produced), metered basis</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2527,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>ACTUAL — EU 205 recompute, 12-mo (EU205_CI)</t>
+          <t>ACTUAL — EU 205 recompute on metered activity data, 12-mo (EU205_CI)</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2543,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>ACTUAL — EU 205 recompute, 12-mo</t>
+          <t>ACTUAL — EU 205 recompute on metered activity data, 12-mo</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2574,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>EXAMPLE — confirm value from ICAO before use</t>
+          <t>EXAMPLE. EU 205 §4.3.9 p.58 sets the transport-market comparator: "Biofuels for transport: 94 g CO2eq/MJ fossil fuel". For an aviation/CORSIA claim the comparator comes from that scheme instead — confirm before use.</t>
         </is>
       </c>
     </row>
